--- a/data/externalStats/File1/RPT_RPT4905554084177SD_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT4905554084177SD_externalStats.xlsx
@@ -2063,7 +2063,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.93445354595572</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -2104,7 +2104,7 @@
         <v>4485152.572008872</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>6502.991610080124</v>
+        <v>6502.991610080125</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454166</v>
+        <v>96.12539893454168</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>630.7031600300147</v>
+        <v>630.7031600300148</v>
       </c>
     </row>
     <row r="31">
@@ -2552,7 +2552,7 @@
         <v>382233.8253246067</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>682.8589505041772</v>
+        <v>682.8589505041771</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -2961,7 +2961,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.39999999999</v>
+        <v>35656.4</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -3292,7 +3292,7 @@
         <v>109743.4473794957</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>41.55721261714</v>
+        <v>41.55721261714001</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -3908,7 +3908,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -3917,28 +3917,28 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>2860.176569160788</v>
+        <v>2860.176569160789</v>
       </c>
       <c r="V53" s="127" t="n">
         <v>1391.766589336762</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1490.435200163811</v>
+        <v>1490.435200163812</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>17.72189602814375</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528717</v>
+        <v>2899.923685528718</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
         <v>9396</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -4079,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X55" s="131" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -4238,7 +4238,7 @@
         <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
-        <v>41.96486816008204</v>
+        <v>41.96486816008203</v>
       </c>
       <c r="N57" s="132" t="n">
         <v>2850.466064366342</v>
@@ -4253,25 +4253,25 @@
         <v>11.50133525344111</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>41.68803870239996</v>
+        <v>41.68803870239995</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681119</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>9.80421488211929</v>
+        <v>9.804214882119291</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>42.13077516565712</v>
+        <v>42.13077516565711</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>2425.769550372533</v>
+        <v>2425.769550372534</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>139916.2470854048</v>
+        <v>139916.2470854047</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>1894.11775226041</v>
@@ -4553,49 +4553,49 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>1879.236665364516</v>
+        <v>1879.236665364515</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>83.07733275588409</v>
+        <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798607</v>
+        <v>5478.965048798606</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310843</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250132</v>
+        <v>2671.817886250133</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423984</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763351</v>
+        <v>4273.151023763352</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>2806.341432842155</v>
+        <v>2806.341432842156</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>57.02415701411741</v>
+        <v>57.02415701411742</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>101.0761670850872</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>7237.592780704711</v>
+        <v>7237.592780704712</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -4715,19 +4715,19 @@
         <v>3051</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2399.052334449065</v>
+        <v>2399.052334449061</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132962</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
@@ -4736,28 +4736,28 @@
         <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844693</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>5515.766545076103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3333.582500652559</v>
+        <v>3333.582500652552</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.67757570038</v>
+        <v>2919.677575700377</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>250.490735587756</v>
+        <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626166</v>
+        <v>6552.046440626156</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5051,7 +5051,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814803</v>
+        <v>22.34085682814804</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -5069,7 +5069,7 @@
         <v>10.15020924840391</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>195.924632515909</v>
+        <v>195.9246325159089</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>2056.782229168566</v>
@@ -5078,7 +5078,7 @@
         <v>1409.31120853687</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>497.2231949594202</v>
+        <v>497.2231949594203</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>10.97973574079871</v>
@@ -5129,7 +5129,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -5138,13 +5138,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229325</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -5336,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765182</v>
+        <v>7.75051817676518</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -5351,10 +5351,10 @@
         <v>12.08636144752263</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>8.192848110463444</v>
+        <v>8.192848110463446</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>4.071420362981854</v>
+        <v>4.071420362981853</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>8.682800100355173</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>3.832345246287814</v>
+        <v>3.832345246287813</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755257</v>
+        <v>7197.985321755255</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -5616,16 +5616,16 @@
         <v>19.05646504017928</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>9732.017604071891</v>
+        <v>9732.017604071889</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625108</v>
+        <v>8157.149229625109</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2891.426278414409</v>
+        <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.9586793554481</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -5634,10 +5634,10 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677067</v>
+        <v>9996.096520677065</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3404.183159089576</v>
+        <v>3404.183159089577</v>
       </c>
       <c r="X75" s="131" t="n">
         <v>96.6647752467498</v>
@@ -5872,7 +5872,7 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.568549907321</v>
+        <v>2209.56854990732</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2593.333683184456</v>
@@ -5887,10 +5887,10 @@
         <v>4839.927367557341</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2292.902614467378</v>
+        <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845832</v>
+        <v>2663.397921845831</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -5899,10 +5899,10 @@
         <v>27.565414861867</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>4995.003831312751</v>
+        <v>4995.003831312752</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -6372,7 +6372,7 @@
         <v>622.0842582708865</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>464872.6830567547</v>
+        <v>464872.6830567548</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>230131.5879723013</v>
@@ -6541,7 +6541,7 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
@@ -6562,19 +6562,19 @@
         <v>1471.956966580286</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>2872.440837634234</v>
+        <v>2872.440837634235</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>1400.449389437117</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>1494.267545410099</v>
+        <v>1494.2675454101</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>17.72189602814375</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.43883087536</v>
+        <v>2912.438830875361</v>
       </c>
     </row>
     <row r="90">
@@ -6675,10 +6675,10 @@
         <v>9396</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -6687,13 +6687,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X91" s="131" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -6809,13 +6809,13 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173875</v>
+        <v>8942.039540173873</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3500.537314860515</v>
+        <v>3500.537314860514</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>78.88548020358266</v>
+        <v>78.88548020358267</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>61.02133320026132</v>
@@ -6827,13 +6827,13 @@
         <v>9792.362202164186</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>3892.812180303247</v>
+        <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888921</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>62.2499783240786</v>
+        <v>62.24997832407858</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>13836.8843754004</v>
@@ -6842,7 +6842,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057687</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -7077,22 +7077,22 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.339040584901</v>
+        <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548971</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361768</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>109.2666359584575</v>
+        <v>109.2666359584576</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778221</v>
+        <v>6423.034571778223</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -7101,16 +7101,16 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960886</v>
+        <v>6613.078984960887</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>5523.444075919048</v>
+        <v>5523.444075919049</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>68.39432747769432</v>
@@ -7244,16 +7244,16 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700392</v>
+        <v>2919.677575700363</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484186</v>
+        <v>6552.808706484156</v>
       </c>
     </row>
     <row r="100">
@@ -7492,7 +7492,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.208591951027</v>
+        <v>522.2085919510268</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -7510,7 +7510,7 @@
         <v>536.567103549567</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>450541.0773560607</v>
+        <v>450541.0773560606</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>219196.1918988632</v>
@@ -7568,7 +7568,7 @@
         <v>247378.9131602585</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>242313.0708691539</v>
+        <v>242313.0708691538</v>
       </c>
       <c r="R104" s="143" t="n">
         <v>3786.655283214763</v>
@@ -7592,7 +7592,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764178</v>
+        <v>504879.6948764177</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8587,7 +8587,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.93445354595572</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>5730185.213893274</v>
+        <v>5730185.213893273</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>8128.782825788127</v>
@@ -8664,7 +8664,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454166</v>
+        <v>96.12539893454168</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -8705,7 +8705,7 @@
         <v>877200.3253680116</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>720.7293338956136</v>
+        <v>720.7293338956135</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>848824.7660158189</v>
+        <v>848824.7660158188</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>193.3559319210432</v>
@@ -9013,7 +9013,7 @@
         <v>581866.6305464627</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>849.15899935381</v>
+        <v>849.1589993538101</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9147,7 +9147,7 @@
         <v>396900.49877657</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>684.9758132507401</v>
+        <v>684.9758132507402</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9485,7 +9485,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.39999999999</v>
+        <v>35656.4</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>877200.3253680116</v>
+        <v>877200.3253680117</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>726.2533367258893</v>
@@ -10432,7 +10432,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -10441,28 +10441,28 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>2860.176569160788</v>
+        <v>2860.176569160789</v>
       </c>
       <c r="V53" s="127" t="n">
         <v>1391.766589336762</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1490.435200163811</v>
+        <v>1490.435200163812</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>17.72189602814375</v>
@@ -10471,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528717</v>
+        <v>2899.923685528718</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -10485,7 +10485,7 @@
         <v>396900.49877657</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>685.0910599231772</v>
+        <v>685.0910599231773</v>
       </c>
     </row>
     <row r="54">
@@ -10591,10 +10591,10 @@
         <v>9396</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -10603,13 +10603,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -10621,10 +10621,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X55" s="131" t="n">
         <v>0</v>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -10762,7 +10762,7 @@
         <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
-        <v>41.96486816008204</v>
+        <v>41.96486816008203</v>
       </c>
       <c r="N57" s="132" t="n">
         <v>2850.466064366342</v>
@@ -10777,25 +10777,25 @@
         <v>11.50133525344111</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>41.68803870239996</v>
+        <v>41.68803870239995</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681119</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>9.80421488211929</v>
+        <v>9.804214882119291</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>42.13077516565712</v>
+        <v>42.13077516565711</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>2425.769550372533</v>
+        <v>2425.769550372534</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -10971,7 +10971,7 @@
         <v>141383.779441519</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>381.6103836297689</v>
+        <v>381.6103836297688</v>
       </c>
     </row>
     <row r="60">
@@ -11077,49 +11077,49 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>1879.236665364516</v>
+        <v>1879.236665364515</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>83.07733275588409</v>
+        <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798607</v>
+        <v>5478.965048798606</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310843</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250132</v>
+        <v>2671.817886250133</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423984</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763351</v>
+        <v>4273.151023763352</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>2806.341432842155</v>
+        <v>2806.341432842156</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>57.02415701411741</v>
+        <v>57.02415701411742</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>101.0761670850872</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>7237.592780704711</v>
+        <v>7237.592780704712</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>95728.40939584021</v>
+        <v>95728.40939584022</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>269.4497581626809</v>
@@ -11239,19 +11239,19 @@
         <v>3051</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2399.052334449065</v>
+        <v>2399.052334449061</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132962</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
@@ -11260,28 +11260,28 @@
         <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844693</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>5515.766545076103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3333.582500652559</v>
+        <v>3333.582500652552</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.67757570038</v>
+        <v>2919.677575700377</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>250.490735587756</v>
+        <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626166</v>
+        <v>6552.046440626156</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11575,7 +11575,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814803</v>
+        <v>22.34085682814804</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -11593,7 +11593,7 @@
         <v>10.15020924840391</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>195.924632515909</v>
+        <v>195.9246325159089</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>2056.782229168566</v>
@@ -11602,7 +11602,7 @@
         <v>1409.31120853687</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>497.2231949594202</v>
+        <v>497.2231949594203</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>10.97973574079871</v>
@@ -11653,7 +11653,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -11662,13 +11662,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229325</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -11860,7 +11860,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765182</v>
+        <v>7.75051817676518</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -11875,10 +11875,10 @@
         <v>12.08636144752263</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>8.192848110463444</v>
+        <v>8.192848110463446</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>4.071420362981854</v>
+        <v>4.071420362981853</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>0</v>
@@ -11893,7 +11893,7 @@
         <v>8.682800100355173</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>3.832345246287814</v>
+        <v>3.832345246287813</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -12128,7 +12128,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755257</v>
+        <v>7197.985321755255</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -12140,16 +12140,16 @@
         <v>19.05646504017928</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>9732.017604071891</v>
+        <v>9732.017604071889</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625108</v>
+        <v>8157.149229625109</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2891.426278414409</v>
+        <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.9586793554481</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -12158,10 +12158,10 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677067</v>
+        <v>9996.096520677065</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3404.183159089576</v>
+        <v>3404.183159089577</v>
       </c>
       <c r="X75" s="131" t="n">
         <v>96.6647752467498</v>
@@ -12396,7 +12396,7 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.568549907321</v>
+        <v>2209.56854990732</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2593.333683184456</v>
@@ -12411,10 +12411,10 @@
         <v>4839.927367557341</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2292.902614467378</v>
+        <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845832</v>
+        <v>2663.397921845831</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -12423,10 +12423,10 @@
         <v>27.565414861867</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>4995.003831312751</v>
+        <v>4995.003831312752</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -12896,7 +12896,7 @@
         <v>622.0842582708865</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>464872.6830567547</v>
+        <v>464872.6830567548</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>230131.5879723013</v>
@@ -13065,7 +13065,7 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
@@ -13086,19 +13086,19 @@
         <v>1471.956966580286</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>2872.440837634234</v>
+        <v>2872.440837634235</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>1400.449389437117</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>1494.267545410099</v>
+        <v>1494.2675454101</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>17.72189602814375</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.43883087536</v>
+        <v>2912.438830875361</v>
       </c>
     </row>
     <row r="90">
@@ -13199,10 +13199,10 @@
         <v>9396</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -13211,13 +13211,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -13229,10 +13229,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X91" s="131" t="n">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -13333,13 +13333,13 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173875</v>
+        <v>8942.039540173873</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3500.537314860515</v>
+        <v>3500.537314860514</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>78.88548020358266</v>
+        <v>78.88548020358267</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>61.02133320026132</v>
@@ -13351,13 +13351,13 @@
         <v>9792.362202164186</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>3892.812180303247</v>
+        <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888921</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>62.2499783240786</v>
+        <v>62.24997832407858</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>13836.8843754004</v>
@@ -13366,7 +13366,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057687</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -13601,22 +13601,22 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.339040584901</v>
+        <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548971</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361768</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>109.2666359584575</v>
+        <v>109.2666359584576</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778221</v>
+        <v>6423.034571778223</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -13625,16 +13625,16 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960886</v>
+        <v>6613.078984960887</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>5523.444075919048</v>
+        <v>5523.444075919049</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>68.39432747769432</v>
@@ -13768,16 +13768,16 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700392</v>
+        <v>2919.677575700363</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484186</v>
+        <v>6552.808706484156</v>
       </c>
     </row>
     <row r="100">
@@ -14016,7 +14016,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.208591951027</v>
+        <v>522.2085919510268</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -14034,7 +14034,7 @@
         <v>536.567103549567</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>450541.0773560607</v>
+        <v>450541.0773560606</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>219196.1918988632</v>
@@ -14092,7 +14092,7 @@
         <v>247378.9131602585</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>242313.0708691539</v>
+        <v>242313.0708691538</v>
       </c>
       <c r="R104" s="143" t="n">
         <v>3786.655283214763</v>
@@ -14116,7 +14116,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764178</v>
+        <v>504879.6948764177</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15111,7 +15111,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.93445354595572</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -15152,7 +15152,7 @@
         <v>7105821.769012147</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>9754.527377416774</v>
+        <v>9754.527377416776</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15188,7 +15188,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454166</v>
+        <v>96.12539893454168</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -15229,7 +15229,7 @@
         <v>1111025.52965187</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>867.3273413215642</v>
+        <v>867.3273413215643</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>867055.9045907295</v>
+        <v>867055.9045907296</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>198.8598248082519</v>
@@ -15534,10 +15534,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>667647.1117400256</v>
+        <v>667647.1117400257</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>942.5664892827295</v>
+        <v>942.5664892827294</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -16009,7 +16009,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.39999999999</v>
+        <v>35656.4</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -16263,7 +16263,7 @@
         <v>130081.0722402474</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>345.2595267693077</v>
+        <v>345.2595267693078</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>127063.6459825253</v>
+        <v>127063.6459825254</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>44.14969160047089</v>
+        <v>44.14969160047088</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -16956,7 +16956,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -16965,28 +16965,28 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>2860.176569160788</v>
+        <v>2860.176569160789</v>
       </c>
       <c r="V53" s="127" t="n">
         <v>1391.766589336762</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1490.435200163811</v>
+        <v>1490.435200163812</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>17.72189602814375</v>
@@ -16995,7 +16995,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528717</v>
+        <v>2899.923685528718</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -17009,7 +17009,7 @@
         <v>415906.9490123874</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>685.3351048132804</v>
+        <v>685.3351048132805</v>
       </c>
     </row>
     <row r="54">
@@ -17115,10 +17115,10 @@
         <v>9396</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -17145,10 +17145,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X55" s="131" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>322418.851610986</v>
+        <v>322418.8516109861</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>533.0386368099751</v>
@@ -17286,7 +17286,7 @@
         <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
-        <v>41.96486816008204</v>
+        <v>41.96486816008203</v>
       </c>
       <c r="N57" s="132" t="n">
         <v>2850.466064366342</v>
@@ -17301,25 +17301,25 @@
         <v>11.50133525344111</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>41.68803870239996</v>
+        <v>41.68803870239995</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681119</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>9.80421488211929</v>
+        <v>9.804214882119291</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>42.13077516565712</v>
+        <v>42.13077516565711</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>2425.769550372533</v>
+        <v>2425.769550372534</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -17601,49 +17601,49 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>1879.236665364516</v>
+        <v>1879.236665364515</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>83.07733275588409</v>
+        <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798607</v>
+        <v>5478.965048798606</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310843</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250132</v>
+        <v>2671.817886250133</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423984</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763351</v>
+        <v>4273.151023763352</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>2806.341432842155</v>
+        <v>2806.341432842156</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>57.02415701411741</v>
+        <v>57.02415701411742</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>101.0761670850872</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>7237.592780704711</v>
+        <v>7237.592780704712</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -17738,7 +17738,7 @@
         <v>107519.0360691012</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>166.0435638400705</v>
+        <v>166.0435638400704</v>
       </c>
     </row>
     <row r="63">
@@ -17763,19 +17763,19 @@
         <v>3051</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2399.052334449065</v>
+        <v>2399.052334449061</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132962</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
@@ -17784,28 +17784,28 @@
         <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844693</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>5515.766545076103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3333.582500652559</v>
+        <v>3333.582500652552</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.67757570038</v>
+        <v>2919.677575700377</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>250.490735587756</v>
+        <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626166</v>
+        <v>6552.046440626156</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17819,7 +17819,7 @@
         <v>105806.2306725778</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>272.6536613951823</v>
+        <v>272.6536613951824</v>
       </c>
     </row>
     <row r="64">
@@ -18099,7 +18099,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814803</v>
+        <v>22.34085682814804</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -18117,7 +18117,7 @@
         <v>10.15020924840391</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>195.924632515909</v>
+        <v>195.9246325159089</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>2056.782229168566</v>
@@ -18126,7 +18126,7 @@
         <v>1409.31120853687</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>497.2231949594202</v>
+        <v>497.2231949594203</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>10.97973574079871</v>
@@ -18177,7 +18177,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -18186,13 +18186,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229325</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -18384,7 +18384,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765182</v>
+        <v>7.75051817676518</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -18399,10 +18399,10 @@
         <v>12.08636144752263</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>8.192848110463444</v>
+        <v>8.192848110463446</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>4.071420362981854</v>
+        <v>4.071420362981853</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>0</v>
@@ -18417,7 +18417,7 @@
         <v>8.682800100355173</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>3.832345246287814</v>
+        <v>3.832345246287813</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -18652,7 +18652,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755257</v>
+        <v>7197.985321755255</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -18664,16 +18664,16 @@
         <v>19.05646504017928</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>9732.017604071891</v>
+        <v>9732.017604071889</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625108</v>
+        <v>8157.149229625109</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2891.426278414409</v>
+        <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.9586793554481</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -18682,10 +18682,10 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677067</v>
+        <v>9996.096520677065</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3404.183159089576</v>
+        <v>3404.183159089577</v>
       </c>
       <c r="X75" s="131" t="n">
         <v>96.6647752467498</v>
@@ -18920,7 +18920,7 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.568549907321</v>
+        <v>2209.56854990732</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2593.333683184456</v>
@@ -18935,10 +18935,10 @@
         <v>4839.927367557341</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2292.902614467378</v>
+        <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845832</v>
+        <v>2663.397921845831</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -18947,10 +18947,10 @@
         <v>27.565414861867</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>4995.003831312751</v>
+        <v>4995.003831312752</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -19420,7 +19420,7 @@
         <v>622.0842582708865</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>464872.6830567547</v>
+        <v>464872.6830567548</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>230131.5879723013</v>
@@ -19589,7 +19589,7 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
@@ -19610,19 +19610,19 @@
         <v>1471.956966580286</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>2872.440837634234</v>
+        <v>2872.440837634235</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>1400.449389437117</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>1494.267545410099</v>
+        <v>1494.2675454101</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>17.72189602814375</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.43883087536</v>
+        <v>2912.438830875361</v>
       </c>
     </row>
     <row r="90">
@@ -19723,10 +19723,10 @@
         <v>9396</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -19735,13 +19735,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -19753,10 +19753,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X91" s="131" t="n">
         <v>0</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -19857,13 +19857,13 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173875</v>
+        <v>8942.039540173873</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3500.537314860515</v>
+        <v>3500.537314860514</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>78.88548020358266</v>
+        <v>78.88548020358267</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>61.02133320026132</v>
@@ -19875,13 +19875,13 @@
         <v>9792.362202164186</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>3892.812180303247</v>
+        <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888921</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>62.2499783240786</v>
+        <v>62.24997832407858</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>13836.8843754004</v>
@@ -19890,7 +19890,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057687</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -20125,22 +20125,22 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.339040584901</v>
+        <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548971</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361768</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>109.2666359584575</v>
+        <v>109.2666359584576</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778221</v>
+        <v>6423.034571778223</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -20149,16 +20149,16 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960886</v>
+        <v>6613.078984960887</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>5523.444075919048</v>
+        <v>5523.444075919049</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>68.39432747769432</v>
@@ -20292,16 +20292,16 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700392</v>
+        <v>2919.677575700363</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484186</v>
+        <v>6552.808706484156</v>
       </c>
     </row>
     <row r="100">
@@ -20540,7 +20540,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.208591951027</v>
+        <v>522.2085919510268</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -20558,7 +20558,7 @@
         <v>536.567103549567</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>450541.0773560607</v>
+        <v>450541.0773560606</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>219196.1918988632</v>
@@ -20616,7 +20616,7 @@
         <v>247378.9131602585</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>242313.0708691539</v>
+        <v>242313.0708691538</v>
       </c>
       <c r="R104" s="143" t="n">
         <v>3786.655283214763</v>
@@ -20640,7 +20640,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764178</v>
+        <v>504879.6948764177</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21635,7 +21635,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.93445354595572</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -21712,7 +21712,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454166</v>
+        <v>96.12539893454168</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>759244.403233764</v>
+        <v>759244.4032337639</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1046.24880310383</v>
@@ -22533,7 +22533,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.39999999999</v>
+        <v>35656.4</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>9492719.166290164</v>
+        <v>9492719.166290166</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>12751.66832098679</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>948484.1838719636</v>
+        <v>948484.1838719635</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1927.909408130234</v>
@@ -23480,7 +23480,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -23489,28 +23489,28 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>2860.176569160788</v>
+        <v>2860.176569160789</v>
       </c>
       <c r="V53" s="127" t="n">
         <v>1391.766589336762</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1490.435200163811</v>
+        <v>1490.435200163812</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>17.72189602814375</v>
@@ -23519,7 +23519,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528717</v>
+        <v>2899.923685528718</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23639,10 +23639,10 @@
         <v>9396</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -23651,13 +23651,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -23669,10 +23669,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X55" s="131" t="n">
         <v>0</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -23810,7 +23810,7 @@
         <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
-        <v>41.96486816008204</v>
+        <v>41.96486816008203</v>
       </c>
       <c r="N57" s="132" t="n">
         <v>2850.466064366342</v>
@@ -23825,25 +23825,25 @@
         <v>11.50133525344111</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>41.68803870239996</v>
+        <v>41.68803870239995</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681119</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>9.80421488211929</v>
+        <v>9.804214882119291</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>42.13077516565712</v>
+        <v>42.13077516565711</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>2425.769550372533</v>
+        <v>2425.769550372534</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -23938,7 +23938,7 @@
         <v>162271.5517438948</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>1424.694944294908</v>
+        <v>1424.694944294909</v>
       </c>
     </row>
     <row r="59">
@@ -24125,49 +24125,49 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>1879.236665364516</v>
+        <v>1879.236665364515</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>83.07733275588409</v>
+        <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798607</v>
+        <v>5478.965048798606</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310843</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250132</v>
+        <v>2671.817886250133</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423984</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763351</v>
+        <v>4273.151023763352</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>2806.341432842155</v>
+        <v>2806.341432842156</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>57.02415701411741</v>
+        <v>57.02415701411742</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>101.0761670850872</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>7237.592780704711</v>
+        <v>7237.592780704712</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -24287,19 +24287,19 @@
         <v>3051</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2399.052334449065</v>
+        <v>2399.052334449061</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132962</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
@@ -24308,28 +24308,28 @@
         <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844693</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>5515.766545076103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3333.582500652559</v>
+        <v>3333.582500652552</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.67757570038</v>
+        <v>2919.677575700377</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>250.490735587756</v>
+        <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626166</v>
+        <v>6552.046440626156</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>35686.01554623179</v>
+        <v>35686.01554623178</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>43.29829418544201</v>
@@ -24623,7 +24623,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814803</v>
+        <v>22.34085682814804</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -24641,7 +24641,7 @@
         <v>10.15020924840391</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>195.924632515909</v>
+        <v>195.9246325159089</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>2056.782229168566</v>
@@ -24650,7 +24650,7 @@
         <v>1409.31120853687</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>497.2231949594202</v>
+        <v>497.2231949594203</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>10.97973574079871</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>34074.63722635455</v>
+        <v>34074.63722635454</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>259.5143090597786</v>
@@ -24701,7 +24701,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -24710,13 +24710,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229325</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -24908,7 +24908,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765182</v>
+        <v>7.75051817676518</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -24923,10 +24923,10 @@
         <v>12.08636144752263</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>8.192848110463444</v>
+        <v>8.192848110463446</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>4.071420362981854</v>
+        <v>4.071420362981853</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
         <v>8.682800100355173</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>3.832345246287814</v>
+        <v>3.832345246287813</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -25176,7 +25176,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755257</v>
+        <v>7197.985321755255</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -25188,16 +25188,16 @@
         <v>19.05646504017928</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>9732.017604071891</v>
+        <v>9732.017604071889</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625108</v>
+        <v>8157.149229625109</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2891.426278414409</v>
+        <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.9586793554481</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -25206,10 +25206,10 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677067</v>
+        <v>9996.096520677065</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3404.183159089576</v>
+        <v>3404.183159089577</v>
       </c>
       <c r="X75" s="131" t="n">
         <v>96.6647752467498</v>
@@ -25444,7 +25444,7 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.568549907321</v>
+        <v>2209.56854990732</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2593.333683184456</v>
@@ -25459,10 +25459,10 @@
         <v>4839.927367557341</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2292.902614467378</v>
+        <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845832</v>
+        <v>2663.397921845831</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -25471,10 +25471,10 @@
         <v>27.565414861867</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>4995.003831312751</v>
+        <v>4995.003831312752</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -25944,7 +25944,7 @@
         <v>622.0842582708865</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>464872.6830567547</v>
+        <v>464872.6830567548</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>230131.5879723013</v>
@@ -26113,7 +26113,7 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
@@ -26134,19 +26134,19 @@
         <v>1471.956966580286</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>2872.440837634234</v>
+        <v>2872.440837634235</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>1400.449389437117</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>1494.267545410099</v>
+        <v>1494.2675454101</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>17.72189602814375</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.43883087536</v>
+        <v>2912.438830875361</v>
       </c>
     </row>
     <row r="90">
@@ -26247,10 +26247,10 @@
         <v>9396</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -26259,13 +26259,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -26277,10 +26277,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X91" s="131" t="n">
         <v>0</v>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -26381,13 +26381,13 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173875</v>
+        <v>8942.039540173873</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3500.537314860515</v>
+        <v>3500.537314860514</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>78.88548020358266</v>
+        <v>78.88548020358267</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>61.02133320026132</v>
@@ -26399,13 +26399,13 @@
         <v>9792.362202164186</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>3892.812180303247</v>
+        <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888921</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>62.2499783240786</v>
+        <v>62.24997832407858</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>13836.8843754004</v>
@@ -26414,7 +26414,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057687</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -26649,22 +26649,22 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.339040584901</v>
+        <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548971</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361768</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>109.2666359584575</v>
+        <v>109.2666359584576</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778221</v>
+        <v>6423.034571778223</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -26673,16 +26673,16 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960886</v>
+        <v>6613.078984960887</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>5523.444075919048</v>
+        <v>5523.444075919049</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>68.39432747769432</v>
@@ -26816,16 +26816,16 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700392</v>
+        <v>2919.677575700363</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484186</v>
+        <v>6552.808706484156</v>
       </c>
     </row>
     <row r="100">
@@ -27064,7 +27064,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.208591951027</v>
+        <v>522.2085919510268</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -27082,7 +27082,7 @@
         <v>536.567103549567</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>450541.0773560607</v>
+        <v>450541.0773560606</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>219196.1918988632</v>
@@ -27140,7 +27140,7 @@
         <v>247378.9131602585</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>242313.0708691539</v>
+        <v>242313.0708691538</v>
       </c>
       <c r="R104" s="143" t="n">
         <v>3786.655283214763</v>
@@ -27164,7 +27164,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764178</v>
+        <v>504879.6948764177</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28159,7 +28159,7 @@
         <v>965679</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>35.93445354595572</v>
+        <v>35.93445354595571</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>30.07689911857227</v>
@@ -28200,7 +28200,7 @@
         <v>10848588.39050994</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>14046.4886195905</v>
+        <v>14046.48861959049</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28236,7 +28236,7 @@
         <v>1189067</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.12539893454166</v>
+        <v>96.12539893454168</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>72.8104218970057</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>872627.0500916672</v>
+        <v>872627.0500916673</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1161.336171445251</v>
@@ -28873,7 +28873,7 @@
         <v>447169.7211032961</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>680.8983455187634</v>
+        <v>680.8983455187633</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -28950,7 +28950,7 @@
         <v>250159.5540040527</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>205.7079113253324</v>
+        <v>205.7079113253325</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -29057,7 +29057,7 @@
         <v>292</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>35656.39999999999</v>
+        <v>35656.4</v>
       </c>
       <c r="F37" s="61" t="n">
         <v>9993</v>
@@ -29388,7 +29388,7 @@
         <v>128360.7324719577</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>262.2820392431559</v>
+        <v>262.2820392431558</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29809,7 +29809,7 @@
         <v>4640556.966857675</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>828.4194522121426</v>
+        <v>828.4194522121425</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -30004,7 +30004,7 @@
         <v>1360.461874663778</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>1442.583703144494</v>
+        <v>1442.583703144493</v>
       </c>
       <c r="L53" s="128" t="n">
         <v>16.81060051458184</v>
@@ -30013,28 +30013,28 @@
         <v>0</v>
       </c>
       <c r="N53" s="129" t="n">
-        <v>2819.856178322854</v>
+        <v>2819.856178322853</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>1374.950469289652</v>
+        <v>1374.950469289653</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>1467.885546217304</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>2860.176569160788</v>
+        <v>2860.176569160789</v>
       </c>
       <c r="V53" s="127" t="n">
         <v>1391.766589336762</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1490.435200163811</v>
+        <v>1490.435200163812</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>17.72189602814375</v>
@@ -30043,7 +30043,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>2899.923685528717</v>
+        <v>2899.923685528718</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30163,10 +30163,10 @@
         <v>9396</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>0</v>
@@ -30175,13 +30175,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P55" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>0</v>
@@ -30193,10 +30193,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X55" s="131" t="n">
         <v>0</v>
@@ -30205,7 +30205,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -30334,7 +30334,7 @@
         <v>13.46605752084745</v>
       </c>
       <c r="M57" s="131" t="n">
-        <v>41.96486816008204</v>
+        <v>41.96486816008203</v>
       </c>
       <c r="N57" s="132" t="n">
         <v>2850.466064366342</v>
@@ -30349,25 +30349,25 @@
         <v>11.50133525344111</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>41.68803870239996</v>
+        <v>41.68803870239995</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>2689.788248383756</v>
+        <v>2689.788248383757</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1409.614172356645</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>964.2203879681115</v>
+        <v>964.2203879681119</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>9.80421488211929</v>
+        <v>9.804214882119291</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>42.13077516565712</v>
+        <v>42.13077516565711</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>2425.769550372533</v>
+        <v>2425.769550372534</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -30649,49 +30649,49 @@
         <v>3454</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>3475.770490677581</v>
+        <v>3475.77049067758</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>1879.236665364516</v>
+        <v>1879.236665364515</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>40.88056000062584</v>
+        <v>40.88056000062586</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>83.07733275588409</v>
+        <v>83.0773327558841</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>5478.965048798607</v>
+        <v>5478.965048798606</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>4130.131957310843</v>
+        <v>4130.131957310844</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>2671.817886250132</v>
+        <v>2671.817886250133</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>54.47014864180036</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>91.05240222120837</v>
+        <v>91.05240222120834</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>6947.472394423984</v>
+        <v>6947.472394423986</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>4273.151023763351</v>
+        <v>4273.151023763352</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>2806.341432842155</v>
+        <v>2806.341432842156</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>57.02415701411741</v>
+        <v>57.02415701411742</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>101.0761670850872</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>7237.592780704711</v>
+        <v>7237.592780704712</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -30811,19 +30811,19 @@
         <v>3051</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2399.052334449065</v>
+        <v>2399.052334449061</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1992.312584988211</v>
+        <v>1992.312584988213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>33.57613890171321</v>
+        <v>33.57613890171319</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>209.6733577939749</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>4634.614416132964</v>
+        <v>4634.614416132962</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>2826.131680913324</v>
@@ -30832,28 +30832,28 @@
         <v>2417.817724958292</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>40.463977920018</v>
+        <v>40.46397792001801</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>231.3531612844695</v>
+        <v>231.3531612844693</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>5515.766545076103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3333.582500652559</v>
+        <v>3333.582500652552</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>2919.67757570038</v>
+        <v>2919.677575700377</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>48.29562868547177</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>250.490735587756</v>
+        <v>250.4907355877558</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>6552.046440626166</v>
+        <v>6552.046440626156</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -31116,7 +31116,7 @@
         <v>36439.43978061579</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>41.27669682992371</v>
+        <v>41.27669682992372</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -31147,7 +31147,7 @@
         <v>1114.495647238112</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>22.34085682814803</v>
+        <v>22.34085682814804</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>193.8046836844156</v>
@@ -31165,7 +31165,7 @@
         <v>10.15020924840391</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>195.924632515909</v>
+        <v>195.9246325159089</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>2056.782229168566</v>
@@ -31174,7 +31174,7 @@
         <v>1409.31120853687</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>497.2231949594202</v>
+        <v>497.2231949594203</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>10.97973574079871</v>
@@ -31225,7 +31225,7 @@
         <v>20484.36177049782</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>7487.078255610651</v>
+        <v>7487.078255610652</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>127.0742137659164</v>
@@ -31234,13 +31234,13 @@
         <v>1779.792258941389</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>29879.92343793609</v>
+        <v>29879.92343793608</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>21054.04803350258</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>8040.775526229323</v>
+        <v>8040.775526229325</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>133.9262247174962</v>
@@ -31432,7 +31432,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>7.750518176765182</v>
+        <v>7.75051817676518</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>4.335843270757449</v>
@@ -31447,10 +31447,10 @@
         <v>12.08636144752263</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>8.192848110463444</v>
+        <v>8.192848110463446</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>4.071420362981854</v>
+        <v>4.071420362981853</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>0</v>
@@ -31465,7 +31465,7 @@
         <v>8.682800100355173</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>3.832345246287814</v>
+        <v>3.832345246287813</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -31700,7 +31700,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7197.985321755257</v>
+        <v>7197.985321755255</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2449.556394593719</v>
@@ -31712,16 +31712,16 @@
         <v>19.05646504017928</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>9732.017604071891</v>
+        <v>9732.017604071889</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8157.149229625108</v>
+        <v>8157.149229625109</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2891.426278414409</v>
+        <v>2891.426278414408</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>77.95867935544808</v>
+        <v>77.9586793554481</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>20.56193962167864</v>
@@ -31730,10 +31730,10 @@
         <v>11147.09612701664</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9996.096520677067</v>
+        <v>9996.096520677065</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3404.183159089576</v>
+        <v>3404.183159089577</v>
       </c>
       <c r="X75" s="131" t="n">
         <v>96.6647752467498</v>
@@ -31968,7 +31968,7 @@
         <v>4438</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2209.568549907321</v>
+        <v>2209.56854990732</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2593.333683184456</v>
@@ -31983,10 +31983,10 @@
         <v>4839.927367557341</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2292.902614467378</v>
+        <v>2292.902614467379</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2663.397921845832</v>
+        <v>2663.397921845831</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>11.13788013767394</v>
@@ -31995,10 +31995,10 @@
         <v>27.565414861867</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>4995.003831312751</v>
+        <v>4995.003831312752</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2339.927961197536</v>
+        <v>2339.927961197535</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2717.102643076893</v>
@@ -32468,7 +32468,7 @@
         <v>622.0842582708865</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>464872.6830567547</v>
+        <v>464872.6830567548</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>230131.5879723013</v>
@@ -32637,7 +32637,7 @@
         <v>2778</v>
       </c>
       <c r="J89" s="127" t="n">
-        <v>1368.212392840543</v>
+        <v>1368.212392840544</v>
       </c>
       <c r="K89" s="128" t="n">
         <v>1446.919546415251</v>
@@ -32658,19 +32658,19 @@
         <v>1471.956966580286</v>
       </c>
       <c r="R89" s="128" t="n">
-        <v>17.34055365383278</v>
+        <v>17.34055365383277</v>
       </c>
       <c r="S89" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>2872.440837634234</v>
+        <v>2872.440837634235</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>1400.449389437117</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>1494.267545410099</v>
+        <v>1494.2675454101</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>17.72189602814375</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>2912.43883087536</v>
+        <v>2912.438830875361</v>
       </c>
     </row>
     <row r="90">
@@ -32771,10 +32771,10 @@
         <v>9396</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>9604.744793221946</v>
+        <v>9604.744793221947</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>7.468734608523375</v>
+        <v>7.468734608523374</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>0</v>
@@ -32783,13 +32783,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>9612.213527830469</v>
+        <v>9612.21352783047</v>
       </c>
       <c r="P91" s="130" t="n">
         <v>9711.100612668353</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>7.681420291833212</v>
+        <v>7.681420291833214</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>0</v>
@@ -32801,10 +32801,10 @@
         <v>9718.782032960187</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>9788.465905473895</v>
+        <v>9788.465905473897</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>7.841870691875749</v>
+        <v>7.841870691875751</v>
       </c>
       <c r="X91" s="131" t="n">
         <v>0</v>
@@ -32813,7 +32813,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>9796.307776165771</v>
+        <v>9796.307776165773</v>
       </c>
     </row>
     <row r="92">
@@ -32905,13 +32905,13 @@
         <v>7305</v>
       </c>
       <c r="J93" s="130" t="n">
-        <v>8942.039540173875</v>
+        <v>8942.039540173873</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3500.537314860515</v>
+        <v>3500.537314860514</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>78.88548020358266</v>
+        <v>78.88548020358267</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>61.02133320026132</v>
@@ -32923,13 +32923,13 @@
         <v>9792.362202164186</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>3892.812180303247</v>
+        <v>3892.812180303246</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>89.4600146088892</v>
+        <v>89.46001460888921</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>62.2499783240786</v>
+        <v>62.24997832407858</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>13836.8843754004</v>
@@ -32938,7 +32938,7 @@
         <v>11405.71069303371</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4368.403547057687</v>
+        <v>4368.403547057689</v>
       </c>
       <c r="X93" s="131" t="n">
         <v>106.4689901288691</v>
@@ -33173,22 +33173,22 @@
         <v>7892</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5685.339040584901</v>
+        <v>5685.3390405849</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>4472.570348548972</v>
+        <v>4472.570348548971</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>51.71639126361766</v>
+        <v>51.71639126361768</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>109.2666359584575</v>
+        <v>109.2666359584576</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>10318.89241635595</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>6423.034571778221</v>
+        <v>6423.034571778223</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>5335.215808095963</v>
@@ -33197,16 +33197,16 @@
         <v>65.6080287794743</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>118.6178170830754</v>
+        <v>118.6178170830753</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>11942.47622573673</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6613.078984960886</v>
+        <v>6613.078984960887</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>5523.444075919048</v>
+        <v>5523.444075919049</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>68.39432747769432</v>
@@ -33340,16 +33340,16 @@
         <v>3333.582500652556</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2919.677575700392</v>
+        <v>2919.677575700363</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>48.29562868547146</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>251.2530014457657</v>
+        <v>251.2530014457652</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>6552.808706484186</v>
+        <v>6552.808706484156</v>
       </c>
     </row>
     <row r="100">
@@ -33588,7 +33588,7 @@
         <v>3516.692006174286</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>522.208591951027</v>
+        <v>522.2085919510268</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>442607.0700834448</v>
@@ -33606,7 +33606,7 @@
         <v>536.567103549567</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>450541.0773560607</v>
+        <v>450541.0773560606</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>219196.1918988632</v>
@@ -33664,7 +33664,7 @@
         <v>247378.9131602585</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>242313.0708691539</v>
+        <v>242313.0708691538</v>
       </c>
       <c r="R104" s="143" t="n">
         <v>3786.655283214763</v>
@@ -33688,7 +33688,7 @@
         <v>2747.025908881708</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>504879.6948764178</v>
+        <v>504879.6948764177</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
